--- a/public/Pod_list.xlsx
+++ b/public/Pod_list.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t>POD -1 (Apex)</t>
   </si>
@@ -22,6 +22,9 @@
     <t>POD-3 (Vertex)</t>
   </si>
   <si>
+    <t>POD-4</t>
+  </si>
+  <si>
     <t>GXO-H&amp;M</t>
   </si>
   <si>
@@ -31,6 +34,9 @@
     <t>Walmart Canada</t>
   </si>
   <si>
+    <t>RIL</t>
+  </si>
+  <si>
     <t>GXO-Apple</t>
   </si>
   <si>
@@ -40,6 +46,9 @@
     <t>Walmart Mexico</t>
   </si>
   <si>
+    <t>RA RMS</t>
+  </si>
+  <si>
     <t>GXO-A&amp;F</t>
   </si>
   <si>
@@ -47,6 +56,9 @@
   </si>
   <si>
     <t>Sam's Club - LAX</t>
+  </si>
+  <si>
+    <t>Case Pick</t>
   </si>
   <si>
     <t>GXO-Verizon</t>
@@ -151,23 +163,24 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <color theme="1"/>
+      <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
       <color theme="1"/>
+      <sz val="11"/>
       <name val="Play"/>
     </font>
     <font>
-      <sz val="11.0"/>
       <color theme="1"/>
+      <sz val="11"/>
       <name val="Play"/>
     </font>
     <font>
@@ -180,7 +193,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -196,7 +209,13 @@
     </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -210,42 +229,42 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -443,17 +462,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="12.63" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="27.0"/>
-    <col customWidth="1" min="3" max="3" width="21.25"/>
+    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="3" max="3" width="21.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -463,172 +483,183 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2">
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
       <c r="B14" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="B15" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>